--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,90 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>razan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>adil</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>razan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>adil</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Registered</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,48 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fenet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>adil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Registered</t>
         </is>
